--- a/data/trans_dic/P21D_2_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P21D_2_R-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria dental, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria dental, no la pudo recibir por motivos económicos (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,12 +572,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,53</t>
+          <t>0,0; 1,44</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,07</t>
+          <t>0,0; 1,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 5,11</t>
+          <t>0,21; 4,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,39</t>
+          <t>0,0; 1,42</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,96</t>
+          <t>1,06; 3,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,88; 5,45</t>
+          <t>1,81; 5,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,77</t>
+          <t>1,76; 3,74</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,41; 9,88</t>
+          <t>3,46; 9,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,02; 8,47</t>
+          <t>1,96; 8,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,99; 7,55</t>
+          <t>3,02; 7,77</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,87</t>
+          <t>0,0; 3,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,85</t>
+          <t>0,63; 2,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,32</t>
+          <t>0,55; 2,35</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,27</t>
+          <t>0,95; 2,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,72</t>
+          <t>1,71; 3,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,72</t>
+          <t>1,42; 2,7</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria dental, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria dental, no la pudo recibir por motivos económicos (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1776</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3420</t>
+          <t>0; 3764</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3850</t>
+          <t>0; 3833</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4417</t>
+          <t>0; 3861</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3709</t>
+          <t>0; 4091</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5497</t>
+          <t>0; 5176</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4453</t>
+          <t>0; 4467</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>163; 4038</t>
+          <t>164; 3899</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6864</t>
+          <t>0; 6994</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5111; 18072</t>
+          <t>4846; 17336</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6367; 18501</t>
+          <t>6154; 17256</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13104; 30008</t>
+          <t>13990; 29772</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7582; 21954</t>
+          <t>7675; 20828</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8398; 35260</t>
+          <t>8157; 35767</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19102; 48242</t>
+          <t>19292; 49616</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4774</t>
+          <t>0; 3825</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2031; 9093</t>
+          <t>2022; 9318</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2698; 10253</t>
+          <t>2426; 10388</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>14492; 36798</t>
+          <t>15415; 38725</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>26156; 57597</t>
+          <t>26499; 55876</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>47199; 86369</t>
+          <t>44969; 85725</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21D_2_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P21D_2_R-Clase-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,87</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,13</t>
+          <t>0,0; 2,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,44</t>
+          <t>0,0; 1,53</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,08</t>
+          <t>0,0; 2,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 4,94</t>
+          <t>0,55; 6,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,3; 2,68</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,8</t>
+          <t>0,88; 3,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,09</t>
+          <t>2,04; 5,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,74</t>
+          <t>1,76; 3,79</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,46; 9,38</t>
+          <t>4,9; 11,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,96; 8,59</t>
+          <t>2,5; 6,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,02; 7,77</t>
+          <t>4,2; 7,65</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,1</t>
+          <t>0,0; 4,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,92</t>
+          <t>0,97; 4,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,35</t>
+          <t>0,84; 3,7</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,39</t>
+          <t>1,54; 3,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,61</t>
+          <t>1,87; 3,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,7</t>
+          <t>1,84; 2,89</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1142</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3764</t>
+          <t>0; 3930</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3833</t>
+          <t>0; 4508</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>926</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>810</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>1736</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3861</t>
+          <t>0; 4571</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4091</t>
+          <t>0; 4104</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5176</t>
+          <t>0; 6030</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>925</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2840</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4467</t>
+          <t>0; 4509</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>164; 3899</t>
+          <t>474; 5402</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6994</t>
+          <t>838; 7375</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>9905</t>
+          <t>9603</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10882</t>
+          <t>13604</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20787</t>
+          <t>23208</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4846; 17336</t>
+          <t>4503; 16882</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6154; 17256</t>
+          <t>7899; 20546</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13990; 29772</t>
+          <t>15820; 34063</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13116</t>
+          <t>21367</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17750</t>
+          <t>15392</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30867</t>
+          <t>36759</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7675; 20828</t>
+          <t>13028; 31532</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8157; 35767</t>
+          <t>9700; 24159</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19292; 49616</t>
+          <t>27499; 50044</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>720</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4648</t>
+          <t>7691</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5365</t>
+          <t>8410</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3825</t>
+          <t>0; 4855</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2022; 9318</t>
+          <t>3432; 17200</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2426; 10388</t>
+          <t>3961; 17512</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>25487</t>
+          <t>33541</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>36433</t>
+          <t>40555</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>74096</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>15415; 38725</t>
+          <t>23542; 46253</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>26499; 55876</t>
+          <t>30729; 53503</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>44969; 85725</t>
+          <t>58347; 91686</t>
         </is>
       </c>
     </row>
